--- a/Schaltpläne/Microcontroller/bom_wearables.xlsx
+++ b/Schaltpläne/Microcontroller/bom_wearables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elias\iCloudDrive\MCI-MedTech\Wearables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C716E1B-CE49-4C29-9D40-B7E319343BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B689E6-E3A5-4D38-9FED-98D51C4A8404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="21509" windowHeight="12810" xr2:uid="{1FE0CD75-BEDB-43A6-8580-0C516C2CBD6A}"/>
+    <workbookView xWindow="-37390" yWindow="-100" windowWidth="21508" windowHeight="11478" xr2:uid="{1FE0CD75-BEDB-43A6-8580-0C516C2CBD6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Supplier</t>
   </si>
@@ -99,6 +99,30 @@
   </si>
   <si>
     <t>Bill of Materials Microcontroller</t>
+  </si>
+  <si>
+    <t>Kondensator 1uF</t>
+  </si>
+  <si>
+    <t>Kondensator 18pF</t>
+  </si>
+  <si>
+    <t>Kondensator 100pF</t>
+  </si>
+  <si>
+    <t>Kondensator 100nF</t>
+  </si>
+  <si>
+    <t>Kondensator 4.7uF</t>
+  </si>
+  <si>
+    <t>Kondensator 4.8 nF</t>
+  </si>
+  <si>
+    <t>Kondensator 12pF</t>
+  </si>
+  <si>
+    <t>Widerstand 4.7kOhm</t>
   </si>
 </sst>
 </file>
@@ -106,7 +130,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -162,14 +186,14 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301851D6-A962-424A-9559-F30595F121AB}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="72.07421875" customWidth="1"/>
@@ -519,26 +543,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
@@ -613,6 +637,70 @@
       </c>
       <c r="H7" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
